--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_30_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_30_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
         <v>13</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,7 +1335,7 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>4</v>
@@ -1923,7 +1923,7 @@
         <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2119,16 +2119,16 @@
         <v>24</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X21" t="n">
         <v>12</v>
@@ -2903,16 +2903,16 @@
         <v>16</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>11</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -3295,16 +3295,16 @@
         <v>21</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X27" t="n">
         <v>7</v>
@@ -3827,16 +3827,16 @@
         <v>91</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X30" t="n">
         <v>41</v>
@@ -4684,7 +4684,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -4880,16 +4880,16 @@
         <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
         <v>3</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>14</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -6056,16 +6056,16 @@
         <v>31</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X44" t="n">
         <v>11</v>
@@ -6252,10 +6252,10 @@
         <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6588,16 +6588,16 @@
         <v>95</v>
       </c>
       <c r="T47" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U47" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X47" t="n">
         <v>38</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_30_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_30_EL.xlsx
@@ -674,10 +674,10 @@
         <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -692,20 +692,20 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>83.67</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>14</v>
       </c>
       <c r="N3" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="O3" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="P3" t="n">
         <v>6</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>64.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1543,10 +1543,10 @@
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
@@ -2131,14 +2131,14 @@
         <v>4</v>
       </c>
       <c r="X21" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="AA21" t="n">
@@ -2915,14 +2915,14 @@
         <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3111,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3307,14 +3307,14 @@
         <v>2</v>
       </c>
       <c r="X27" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
@@ -3351,14 +3351,14 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -3503,14 +3503,14 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>8</v>
       </c>
       <c r="X30" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="Y30" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3872,25 +3872,25 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4304,14 +4304,14 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4696,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -4892,14 +4892,14 @@
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5284,14 +5284,14 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,10 +5480,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -5676,14 +5676,14 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -6068,14 +6068,14 @@
         <v>3</v>
       </c>
       <c r="X44" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Y44" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6264,14 +6264,14 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA45" t="n">
@@ -6600,14 +6600,14 @@
         <v>4</v>
       </c>
       <c r="X47" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="Y47" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="AA47" t="n">
